--- a/보고서/독학기숙.xlsx
+++ b/보고서/독학기숙.xlsx
@@ -26,7 +26,7 @@
     <t>데이터 기준일자</t>
   </si>
   <si>
-    <t>2026-06-14</t>
+    <t>2026-06-21</t>
   </si>
   <si>
     <t xml:space="preserve">캠페인 정보 </t>
@@ -59,7 +59,7 @@
     <t xml:space="preserve">총 조회수 </t>
   </si>
   <si>
-    <t>724 (pv)</t>
+    <t>944 (pv)</t>
   </si>
   <si>
     <t xml:space="preserve">30일간 누적 조회수 </t>
@@ -68,7 +68,7 @@
     <t xml:space="preserve">일일 평균 조회수 </t>
   </si>
   <si>
-    <t>28 (pv)</t>
+    <t>29 (pv)</t>
   </si>
   <si>
     <t>유입 키워드 TOP 10</t>
@@ -83,10 +83,13 @@
     <t>비율(%)</t>
   </si>
   <si>
+    <t>이투스247독학기숙학원</t>
+  </si>
+  <si>
     <t>이투스 247 기숙 광주</t>
   </si>
   <si>
-    <t>이투스247독학기숙학원</t>
+    <t>광주 이투스 기숙학원</t>
   </si>
   <si>
     <t>경기 광주 이투스247 독학기숙학원</t>
@@ -101,16 +104,13 @@
     <t>경기 광주 이투스247 독학기숙학원 하루루틴</t>
   </si>
   <si>
-    <t>광주 이투스 기숙학원</t>
-  </si>
-  <si>
     <t>이투스 247 독학재수기숙</t>
   </si>
   <si>
     <t>광주 이투스 247 기숙학원</t>
   </si>
   <si>
-    <t>기숙학원</t>
+    <t>이투스 광주기숙학원 비용</t>
   </si>
   <si>
     <t>신청자 통계</t>
@@ -188,7 +188,7 @@
     <t>일별 콘텐츠 조회수</t>
   </si>
   <si>
-    <t>날짜(2026.03.15~2026.06.14)</t>
+    <t>날짜(2026.03.22~2026.06.21)</t>
   </si>
   <si>
     <t>요일</t>
@@ -206,40 +206,61 @@
     <t>일</t>
   </si>
   <si>
-    <t>2026-06-13</t>
+    <t>2026-06-20</t>
   </si>
   <si>
     <t>토</t>
   </si>
   <si>
-    <t>2026-06-12</t>
+    <t>2026-06-19</t>
   </si>
   <si>
     <t>금</t>
   </si>
   <si>
-    <t>2026-06-11</t>
+    <t>2026-06-18</t>
   </si>
   <si>
     <t>목</t>
   </si>
   <si>
-    <t>2026-06-10</t>
+    <t>2026-06-17</t>
   </si>
   <si>
     <t>수</t>
   </si>
   <si>
-    <t>2026-06-09</t>
+    <t>2026-06-16</t>
   </si>
   <si>
     <t>화</t>
   </si>
   <si>
-    <t>2026-06-08</t>
+    <t>2026-06-15</t>
   </si>
   <si>
     <t>월</t>
+  </si>
+  <si>
+    <t>2026-06-14</t>
+  </si>
+  <si>
+    <t>2026-06-13</t>
+  </si>
+  <si>
+    <t>2026-06-12</t>
+  </si>
+  <si>
+    <t>2026-06-11</t>
+  </si>
+  <si>
+    <t>2026-06-10</t>
+  </si>
+  <si>
+    <t>2026-06-09</t>
+  </si>
+  <si>
+    <t>2026-06-08</t>
   </si>
   <si>
     <t>2026-06-07</t>
@@ -476,27 +497,6 @@
     <t>2026-03-22</t>
   </si>
   <si>
-    <t>2026-03-21</t>
-  </si>
-  <si>
-    <t>2026-03-20</t>
-  </si>
-  <si>
-    <t>2026-03-19</t>
-  </si>
-  <si>
-    <t>2026-03-18</t>
-  </si>
-  <si>
-    <t>2026-03-17</t>
-  </si>
-  <si>
-    <t>2026-03-16</t>
-  </si>
-  <si>
-    <t>2026-03-15</t>
-  </si>
-  <si>
     <t>콘텐츠 목록</t>
   </si>
   <si>
@@ -515,13 +515,13 @@
     <t>댓글</t>
   </si>
   <si>
-    <t>경기 광주 이투스247 독학기숙학원 하루루틴 | 반수성공반 14시간 순공 만드는 독학기숙 시스템</t>
+    <t>이투스247 독학기숙학원 경기광주점 독학기숙의 몰입 환경이 인상적이었던 곳</t>
   </si>
   <si>
-    <t>호세아1</t>
+    <t>하준마마</t>
   </si>
   <si>
-    <t>https://blog.naver.com/hoshea1/224294340079</t>
+    <t>https://blog.naver.com/em2868/224304983862?fromRss=true&amp;trackingCode=rss</t>
   </si>
   <si>
     <t>이투스247 독학기숙학원 경기광주 직접 방문 후기 | 재수기숙학원 추천</t>
@@ -533,13 +533,13 @@
     <t>https://blog.naver.com/jwp3214/224303667337?fromRss=true&amp;trackingCode=rss</t>
   </si>
   <si>
-    <t>이투스247 독학기숙학원 경기광주점 독학기숙의 몰입 환경이 인상적이었던 곳</t>
+    <t>경기 광주 이투스247 독학기숙학원 하루루틴 | 반수성공반 14시간 순공 만드는 독학기숙 시스템</t>
   </si>
   <si>
-    <t>하준마마</t>
+    <t>호세아1</t>
   </si>
   <si>
-    <t>https://blog.naver.com/em2868/224304983862?fromRss=true&amp;trackingCode=rss</t>
+    <t>https://blog.naver.com/hoshea1/224294340079</t>
   </si>
   <si>
     <t>재수기숙학원 추천 이투스247독학기숙학원 경기광주</t>
@@ -1899,7 +1899,7 @@
       </c>
       <c r="E20" s="43"/>
       <c r="F20" s="43">
-        <v>0.16666666666667</v>
+        <v>0.19512195121951</v>
       </c>
       <c r="G20" s="24"/>
     </row>
@@ -1914,7 +1914,7 @@
       <c r="D21" s="27"/>
       <c r="E21" s="46"/>
       <c r="F21" s="46">
-        <v>0.13888888888889</v>
+        <v>0.14634146341463</v>
       </c>
       <c r="G21" s="24"/>
     </row>
@@ -1928,7 +1928,7 @@
       </c>
       <c r="E22" s="43"/>
       <c r="F22" s="43">
-        <v>0.11111111111111</v>
+        <v>0.1219512195122</v>
       </c>
       <c r="G22" s="24"/>
     </row>
@@ -1943,7 +1943,7 @@
       <c r="D23" s="27"/>
       <c r="E23" s="46"/>
       <c r="F23" s="46">
-        <v>0.11111111111111</v>
+        <v>0.097560975609756</v>
       </c>
       <c r="G23" s="24"/>
     </row>
@@ -1957,7 +1957,7 @@
       </c>
       <c r="E24" s="43"/>
       <c r="F24" s="43">
-        <v>0.11111111111111</v>
+        <v>0.097560975609756</v>
       </c>
       <c r="G24" s="24"/>
     </row>
@@ -1972,7 +1972,7 @@
       <c r="D25" s="27"/>
       <c r="E25" s="46"/>
       <c r="F25" s="46">
-        <v>0.083333333333333</v>
+        <v>0.097560975609756</v>
       </c>
       <c r="G25" s="24"/>
     </row>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="E26" s="43"/>
       <c r="F26" s="43">
-        <v>0.083333333333333</v>
+        <v>0.073170731707317</v>
       </c>
       <c r="G26" s="24"/>
     </row>
@@ -2001,7 +2001,7 @@
       <c r="D27" s="27"/>
       <c r="E27" s="46"/>
       <c r="F27" s="46">
-        <v>0.083333333333333</v>
+        <v>0.073170731707317</v>
       </c>
       <c r="G27" s="24"/>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="E28" s="43"/>
       <c r="F28" s="43">
-        <v>0.055555555555556</v>
+        <v>0.048780487804878</v>
       </c>
       <c r="G28" s="24"/>
     </row>
@@ -2030,7 +2030,7 @@
       <c r="D29" s="37"/>
       <c r="E29" s="49"/>
       <c r="F29" s="49">
-        <v>0.055555555555556</v>
+        <v>0.048780487804878</v>
       </c>
       <c r="G29" s="24"/>
     </row>
@@ -3408,10 +3408,10 @@
         <v>7</v>
       </c>
       <c r="F3" s="82">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G3" s="82">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="Z3" s="83"/>
     </row>
@@ -3425,13 +3425,13 @@
         <v>63</v>
       </c>
       <c r="E4" s="86">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F4" s="86">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="G4" s="86">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="Z4" s="83"/>
     </row>
@@ -3445,13 +3445,13 @@
         <v>65</v>
       </c>
       <c r="E5" s="82">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F5" s="82">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="G5" s="82">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="Z5" s="83"/>
     </row>
@@ -3465,13 +3465,13 @@
         <v>67</v>
       </c>
       <c r="E6" s="86">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F6" s="86">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="G6" s="86">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="Z6" s="83"/>
     </row>
@@ -3485,13 +3485,13 @@
         <v>69</v>
       </c>
       <c r="E7" s="82">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F7" s="82">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="G7" s="82">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="Z7" s="83"/>
     </row>
@@ -3505,13 +3505,13 @@
         <v>71</v>
       </c>
       <c r="E8" s="86">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F8" s="86">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="G8" s="86">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="Z8" s="83"/>
     </row>
@@ -3525,13 +3525,13 @@
         <v>73</v>
       </c>
       <c r="E9" s="82">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F9" s="82">
         <v>29</v>
       </c>
       <c r="G9" s="82">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="Z9" s="83"/>
     </row>
@@ -3545,13 +3545,13 @@
         <v>61</v>
       </c>
       <c r="E10" s="86">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="F10" s="86">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="G10" s="86">
-        <v>71</v>
+        <v>39</v>
       </c>
       <c r="Z10" s="83"/>
     </row>
@@ -3565,13 +3565,13 @@
         <v>63</v>
       </c>
       <c r="E11" s="82">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F11" s="82">
+        <v>33</v>
+      </c>
+      <c r="G11" s="82">
         <v>41</v>
-      </c>
-      <c r="G11" s="82">
-        <v>52</v>
       </c>
       <c r="Z11" s="83"/>
     </row>
@@ -3588,10 +3588,10 @@
         <v>12</v>
       </c>
       <c r="F12" s="86">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G12" s="86">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="Z12" s="83"/>
     </row>
@@ -3605,13 +3605,13 @@
         <v>67</v>
       </c>
       <c r="E13" s="82">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F13" s="82">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="G13" s="82">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="Z13" s="83"/>
     </row>
@@ -3625,13 +3625,13 @@
         <v>69</v>
       </c>
       <c r="E14" s="86">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F14" s="86">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G14" s="86">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="Z14" s="83"/>
     </row>
@@ -3645,13 +3645,13 @@
         <v>71</v>
       </c>
       <c r="E15" s="82">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F15" s="82">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="G15" s="82">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="Z15" s="83"/>
     </row>
@@ -3665,13 +3665,13 @@
         <v>73</v>
       </c>
       <c r="E16" s="86">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="F16" s="86">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="G16" s="86">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="Z16" s="83"/>
     </row>
@@ -3685,13 +3685,13 @@
         <v>61</v>
       </c>
       <c r="E17" s="82">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="F17" s="82">
-        <v>5</v>
+        <v>52</v>
       </c>
       <c r="G17" s="82">
-        <v>9</v>
+        <v>71</v>
       </c>
       <c r="Z17" s="83"/>
     </row>
@@ -3705,13 +3705,13 @@
         <v>63</v>
       </c>
       <c r="E18" s="86">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="F18" s="86">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="G18" s="86">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="Z18" s="83"/>
     </row>
@@ -3725,13 +3725,13 @@
         <v>65</v>
       </c>
       <c r="E19" s="82">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F19" s="82">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="G19" s="82">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="Z19" s="83"/>
     </row>
@@ -3745,13 +3745,13 @@
         <v>67</v>
       </c>
       <c r="E20" s="86">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F20" s="86">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G20" s="86">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Z20" s="83"/>
     </row>
@@ -3765,13 +3765,13 @@
         <v>69</v>
       </c>
       <c r="E21" s="82">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F21" s="82">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="G21" s="82">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="Z21" s="83"/>
     </row>
@@ -3785,13 +3785,13 @@
         <v>71</v>
       </c>
       <c r="E22" s="86">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="F22" s="86">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="G22" s="86">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="Z22" s="83"/>
     </row>
@@ -3805,13 +3805,13 @@
         <v>73</v>
       </c>
       <c r="E23" s="82">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F23" s="82">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="G23" s="82">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="Z23" s="83"/>
     </row>
@@ -3825,13 +3825,13 @@
         <v>61</v>
       </c>
       <c r="E24" s="86">
+        <v>4</v>
+      </c>
+      <c r="F24" s="86">
         <v>5</v>
       </c>
-      <c r="F24" s="86">
-        <v>12</v>
-      </c>
       <c r="G24" s="86">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="Z24" s="83"/>
     </row>
@@ -3845,13 +3845,13 @@
         <v>63</v>
       </c>
       <c r="E25" s="82">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="F25" s="82">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G25" s="82">
-        <v>46</v>
+        <v>9</v>
       </c>
       <c r="Z25" s="83"/>
     </row>
@@ -3865,13 +3865,13 @@
         <v>65</v>
       </c>
       <c r="E26" s="86">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F26" s="86">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G26" s="86">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Z26" s="83"/>
     </row>
@@ -3885,13 +3885,13 @@
         <v>67</v>
       </c>
       <c r="E27" s="82">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F27" s="82">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G27" s="82">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z27" s="83"/>
     </row>
@@ -3905,13 +3905,13 @@
         <v>69</v>
       </c>
       <c r="E28" s="86">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F28" s="86">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G28" s="86">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z28" s="83"/>
     </row>
@@ -3925,13 +3925,13 @@
         <v>71</v>
       </c>
       <c r="E29" s="82">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F29" s="82">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G29" s="82">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Z29" s="83"/>
     </row>
@@ -3945,13 +3945,13 @@
         <v>73</v>
       </c>
       <c r="E30" s="86">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F30" s="86">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G30" s="86">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="Z30" s="83"/>
     </row>
@@ -3965,13 +3965,13 @@
         <v>61</v>
       </c>
       <c r="E31" s="82">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F31" s="82">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G31" s="82">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Z31" s="83"/>
     </row>
@@ -3985,13 +3985,13 @@
         <v>63</v>
       </c>
       <c r="E32" s="86">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F32" s="86">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G32" s="86">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="Z32" s="83"/>
     </row>
@@ -13553,13 +13553,13 @@
         <v>166</v>
       </c>
       <c r="D3" s="94" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E3" s="24">
-        <v>111</v>
+        <v>11</v>
       </c>
       <c r="F3" s="24">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G3" s="95"/>
       <c r="H3" s="89"/>
@@ -13587,7 +13587,7 @@
         <v>169</v>
       </c>
       <c r="D5" s="99" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="E5" s="98">
         <v>4</v>
@@ -13621,13 +13621,13 @@
         <v>172</v>
       </c>
       <c r="D7" s="94" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="E7" s="24">
-        <v>11</v>
+        <v>111</v>
       </c>
       <c r="F7" s="24">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G7" s="95"/>
       <c r="H7" s="89"/>
@@ -13655,7 +13655,7 @@
         <v>175</v>
       </c>
       <c r="D9" s="99" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="E9" s="98">
         <v>0</v>

--- a/보고서/독학기숙.xlsx
+++ b/보고서/독학기숙.xlsx
@@ -26,7 +26,7 @@
     <t>데이터 기준일자</t>
   </si>
   <si>
-    <t>2026-06-21</t>
+    <t>2026-08-18</t>
   </si>
   <si>
     <t xml:space="preserve">캠페인 정보 </t>
@@ -59,16 +59,19 @@
     <t xml:space="preserve">총 조회수 </t>
   </si>
   <si>
-    <t>944 (pv)</t>
+    <t>1,701 (pv)</t>
   </si>
   <si>
     <t xml:space="preserve">30일간 누적 조회수 </t>
   </si>
   <si>
+    <t>190 (pv)</t>
+  </si>
+  <si>
     <t xml:space="preserve">일일 평균 조회수 </t>
   </si>
   <si>
-    <t>29 (pv)</t>
+    <t>19 (pv)</t>
   </si>
   <si>
     <t>유입 키워드 TOP 10</t>
@@ -89,7 +92,16 @@
     <t>이투스 247 기숙 광주</t>
   </si>
   <si>
+    <t>이투스 독학기숙학원 광주</t>
+  </si>
+  <si>
     <t>광주 이투스 기숙학원</t>
+  </si>
+  <si>
+    <t>이투스독학기숙</t>
+  </si>
+  <si>
+    <t>이투스 광주</t>
   </si>
   <si>
     <t>경기 광주 이투스247 독학기숙학원</t>
@@ -98,19 +110,10 @@
     <t>이투스기숙학원</t>
   </si>
   <si>
-    <t>이투스독학기숙</t>
-  </si>
-  <si>
-    <t>경기 광주 이투스247 독학기숙학원 하루루틴</t>
-  </si>
-  <si>
     <t>이투스 247 독학재수기숙</t>
   </si>
   <si>
-    <t>광주 이투스 247 기숙학원</t>
-  </si>
-  <si>
-    <t>이투스 광주기숙학원 비용</t>
+    <t>광주기숙학원</t>
   </si>
   <si>
     <t>신청자 통계</t>
@@ -188,7 +191,7 @@
     <t>일별 콘텐츠 조회수</t>
   </si>
   <si>
-    <t>날짜(2026.03.22~2026.06.21)</t>
+    <t>날짜(2026.05.19~2026.08.18)</t>
   </si>
   <si>
     <t>요일</t>
@@ -203,43 +206,217 @@
     <t>합산 조회수(PC+Mobile)</t>
   </si>
   <si>
+    <t>화</t>
+  </si>
+  <si>
+    <t>2026-08-17</t>
+  </si>
+  <si>
+    <t>월</t>
+  </si>
+  <si>
+    <t>2026-08-16</t>
+  </si>
+  <si>
     <t>일</t>
+  </si>
+  <si>
+    <t>2026-08-15</t>
+  </si>
+  <si>
+    <t>토</t>
+  </si>
+  <si>
+    <t>2026-08-14</t>
+  </si>
+  <si>
+    <t>금</t>
+  </si>
+  <si>
+    <t>2026-08-13</t>
+  </si>
+  <si>
+    <t>목</t>
+  </si>
+  <si>
+    <t>2026-08-12</t>
+  </si>
+  <si>
+    <t>수</t>
+  </si>
+  <si>
+    <t>2026-08-11</t>
+  </si>
+  <si>
+    <t>2026-08-10</t>
+  </si>
+  <si>
+    <t>2026-08-09</t>
+  </si>
+  <si>
+    <t>2026-08-08</t>
+  </si>
+  <si>
+    <t>2026-08-07</t>
+  </si>
+  <si>
+    <t>2026-08-06</t>
+  </si>
+  <si>
+    <t>2026-08-05</t>
+  </si>
+  <si>
+    <t>2026-08-04</t>
+  </si>
+  <si>
+    <t>2026-08-03</t>
+  </si>
+  <si>
+    <t>2026-08-02</t>
+  </si>
+  <si>
+    <t>2026-08-01</t>
+  </si>
+  <si>
+    <t>2026-07-31</t>
+  </si>
+  <si>
+    <t>2026-07-30</t>
+  </si>
+  <si>
+    <t>2026-07-29</t>
+  </si>
+  <si>
+    <t>2026-07-28</t>
+  </si>
+  <si>
+    <t>2026-07-27</t>
+  </si>
+  <si>
+    <t>2026-07-26</t>
+  </si>
+  <si>
+    <t>2026-07-25</t>
+  </si>
+  <si>
+    <t>2026-07-24</t>
+  </si>
+  <si>
+    <t>2026-07-23</t>
+  </si>
+  <si>
+    <t>2026-07-22</t>
+  </si>
+  <si>
+    <t>2026-07-21</t>
+  </si>
+  <si>
+    <t>2026-07-20</t>
+  </si>
+  <si>
+    <t>2026-07-19</t>
+  </si>
+  <si>
+    <t>2026-07-18</t>
+  </si>
+  <si>
+    <t>2026-07-17</t>
+  </si>
+  <si>
+    <t>2026-07-16</t>
+  </si>
+  <si>
+    <t>2026-07-15</t>
+  </si>
+  <si>
+    <t>2026-07-14</t>
+  </si>
+  <si>
+    <t>2026-07-13</t>
+  </si>
+  <si>
+    <t>2026-07-12</t>
+  </si>
+  <si>
+    <t>2026-07-11</t>
+  </si>
+  <si>
+    <t>2026-07-10</t>
+  </si>
+  <si>
+    <t>2026-07-09</t>
+  </si>
+  <si>
+    <t>2026-07-08</t>
+  </si>
+  <si>
+    <t>2026-07-07</t>
+  </si>
+  <si>
+    <t>2026-07-06</t>
+  </si>
+  <si>
+    <t>2026-07-05</t>
+  </si>
+  <si>
+    <t>2026-07-04</t>
+  </si>
+  <si>
+    <t>2026-07-03</t>
+  </si>
+  <si>
+    <t>2026-07-02</t>
+  </si>
+  <si>
+    <t>2026-07-01</t>
+  </si>
+  <si>
+    <t>2026-06-30</t>
+  </si>
+  <si>
+    <t>2026-06-29</t>
+  </si>
+  <si>
+    <t>2026-06-28</t>
+  </si>
+  <si>
+    <t>2026-06-27</t>
+  </si>
+  <si>
+    <t>2026-06-26</t>
+  </si>
+  <si>
+    <t>2026-06-25</t>
+  </si>
+  <si>
+    <t>2026-06-24</t>
+  </si>
+  <si>
+    <t>2026-06-23</t>
+  </si>
+  <si>
+    <t>2026-06-22</t>
+  </si>
+  <si>
+    <t>2026-06-21</t>
   </si>
   <si>
     <t>2026-06-20</t>
   </si>
   <si>
-    <t>토</t>
-  </si>
-  <si>
     <t>2026-06-19</t>
-  </si>
-  <si>
-    <t>금</t>
   </si>
   <si>
     <t>2026-06-18</t>
   </si>
   <si>
-    <t>목</t>
-  </si>
-  <si>
     <t>2026-06-17</t>
-  </si>
-  <si>
-    <t>수</t>
   </si>
   <si>
     <t>2026-06-16</t>
   </si>
   <si>
-    <t>화</t>
-  </si>
-  <si>
     <t>2026-06-15</t>
-  </si>
-  <si>
-    <t>월</t>
   </si>
   <si>
     <t>2026-06-14</t>
@@ -323,180 +500,6 @@
     <t>2026-05-19</t>
   </si>
   <si>
-    <t>2026-05-18</t>
-  </si>
-  <si>
-    <t>2026-05-17</t>
-  </si>
-  <si>
-    <t>2026-05-16</t>
-  </si>
-  <si>
-    <t>2026-05-15</t>
-  </si>
-  <si>
-    <t>2026-05-14</t>
-  </si>
-  <si>
-    <t>2026-05-13</t>
-  </si>
-  <si>
-    <t>2026-05-12</t>
-  </si>
-  <si>
-    <t>2026-05-11</t>
-  </si>
-  <si>
-    <t>2026-05-10</t>
-  </si>
-  <si>
-    <t>2026-05-09</t>
-  </si>
-  <si>
-    <t>2026-05-08</t>
-  </si>
-  <si>
-    <t>2026-05-07</t>
-  </si>
-  <si>
-    <t>2026-05-06</t>
-  </si>
-  <si>
-    <t>2026-05-05</t>
-  </si>
-  <si>
-    <t>2026-05-04</t>
-  </si>
-  <si>
-    <t>2026-05-03</t>
-  </si>
-  <si>
-    <t>2026-05-02</t>
-  </si>
-  <si>
-    <t>2026-05-01</t>
-  </si>
-  <si>
-    <t>2026-04-30</t>
-  </si>
-  <si>
-    <t>2026-04-29</t>
-  </si>
-  <si>
-    <t>2026-04-28</t>
-  </si>
-  <si>
-    <t>2026-04-27</t>
-  </si>
-  <si>
-    <t>2026-04-26</t>
-  </si>
-  <si>
-    <t>2026-04-25</t>
-  </si>
-  <si>
-    <t>2026-04-24</t>
-  </si>
-  <si>
-    <t>2026-04-23</t>
-  </si>
-  <si>
-    <t>2026-04-22</t>
-  </si>
-  <si>
-    <t>2026-04-21</t>
-  </si>
-  <si>
-    <t>2026-04-20</t>
-  </si>
-  <si>
-    <t>2026-04-19</t>
-  </si>
-  <si>
-    <t>2026-04-18</t>
-  </si>
-  <si>
-    <t>2026-04-17</t>
-  </si>
-  <si>
-    <t>2026-04-16</t>
-  </si>
-  <si>
-    <t>2026-04-15</t>
-  </si>
-  <si>
-    <t>2026-04-14</t>
-  </si>
-  <si>
-    <t>2026-04-13</t>
-  </si>
-  <si>
-    <t>2026-04-12</t>
-  </si>
-  <si>
-    <t>2026-04-11</t>
-  </si>
-  <si>
-    <t>2026-04-10</t>
-  </si>
-  <si>
-    <t>2026-04-09</t>
-  </si>
-  <si>
-    <t>2026-04-08</t>
-  </si>
-  <si>
-    <t>2026-04-07</t>
-  </si>
-  <si>
-    <t>2026-04-06</t>
-  </si>
-  <si>
-    <t>2026-04-05</t>
-  </si>
-  <si>
-    <t>2026-04-04</t>
-  </si>
-  <si>
-    <t>2026-04-03</t>
-  </si>
-  <si>
-    <t>2026-04-02</t>
-  </si>
-  <si>
-    <t>2026-04-01</t>
-  </si>
-  <si>
-    <t>2026-03-31</t>
-  </si>
-  <si>
-    <t>2026-03-30</t>
-  </si>
-  <si>
-    <t>2026-03-29</t>
-  </si>
-  <si>
-    <t>2026-03-28</t>
-  </si>
-  <si>
-    <t>2026-03-27</t>
-  </si>
-  <si>
-    <t>2026-03-26</t>
-  </si>
-  <si>
-    <t>2026-03-25</t>
-  </si>
-  <si>
-    <t>2026-03-24</t>
-  </si>
-  <si>
-    <t>2026-03-23</t>
-  </si>
-  <si>
-    <t>2026-03-22</t>
-  </si>
-  <si>
     <t>콘텐츠 목록</t>
   </si>
   <si>
@@ -564,9 +567,6 @@
   </si>
   <si>
     <t>광주 독학기숙학원</t>
-  </si>
-  <si>
-    <t>광주기숙학원</t>
   </si>
   <si>
     <t>이투스247 독학기숙학원</t>
@@ -1834,7 +1834,7 @@
         <v>14</v>
       </c>
       <c r="C15" s="32" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D15" s="33"/>
       <c r="E15" s="33"/>
@@ -1844,10 +1844,10 @@
     <row r="16" spans="1:26" customHeight="1" ht="15">
       <c r="A16" s="3"/>
       <c r="B16" s="21" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C16" s="35" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D16" s="36"/>
       <c r="E16" s="36"/>
@@ -1866,7 +1866,7 @@
     <row r="18" spans="1:26" customHeight="1" ht="19.5">
       <c r="A18" s="24"/>
       <c r="B18" s="25" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C18" s="26"/>
       <c r="D18" s="26"/>
@@ -1877,15 +1877,15 @@
     <row r="19" spans="1:26" customHeight="1" ht="15">
       <c r="A19" s="24"/>
       <c r="B19" s="38" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C19" s="39" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D19" s="40"/>
       <c r="E19" s="38"/>
       <c r="F19" s="38" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G19" s="24"/>
     </row>
@@ -1895,11 +1895,11 @@
         <v>1</v>
       </c>
       <c r="C20" s="42" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E20" s="43"/>
       <c r="F20" s="43">
-        <v>0.19512195121951</v>
+        <v>0.19642857142857</v>
       </c>
       <c r="G20" s="24"/>
     </row>
@@ -1909,12 +1909,12 @@
         <v>2</v>
       </c>
       <c r="C21" s="45" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D21" s="27"/>
       <c r="E21" s="46"/>
       <c r="F21" s="46">
-        <v>0.14634146341463</v>
+        <v>0.17857142857143</v>
       </c>
       <c r="G21" s="24"/>
     </row>
@@ -1924,11 +1924,11 @@
         <v>3</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E22" s="43"/>
       <c r="F22" s="43">
-        <v>0.1219512195122</v>
+        <v>0.10714285714286</v>
       </c>
       <c r="G22" s="24"/>
     </row>
@@ -1938,12 +1938,12 @@
         <v>4</v>
       </c>
       <c r="C23" s="45" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D23" s="27"/>
       <c r="E23" s="46"/>
       <c r="F23" s="46">
-        <v>0.097560975609756</v>
+        <v>0.10714285714286</v>
       </c>
       <c r="G23" s="24"/>
     </row>
@@ -1953,11 +1953,11 @@
         <v>5</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E24" s="43"/>
       <c r="F24" s="43">
-        <v>0.097560975609756</v>
+        <v>0.089285714285714</v>
       </c>
       <c r="G24" s="24"/>
     </row>
@@ -1967,12 +1967,12 @@
         <v>6</v>
       </c>
       <c r="C25" s="45" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D25" s="27"/>
       <c r="E25" s="46"/>
       <c r="F25" s="46">
-        <v>0.097560975609756</v>
+        <v>0.071428571428571</v>
       </c>
       <c r="G25" s="24"/>
     </row>
@@ -1982,11 +1982,11 @@
         <v>7</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E26" s="43"/>
       <c r="F26" s="43">
-        <v>0.073170731707317</v>
+        <v>0.071428571428571</v>
       </c>
       <c r="G26" s="24"/>
     </row>
@@ -1996,12 +1996,12 @@
         <v>8</v>
       </c>
       <c r="C27" s="45" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D27" s="27"/>
       <c r="E27" s="46"/>
       <c r="F27" s="46">
-        <v>0.073170731707317</v>
+        <v>0.071428571428571</v>
       </c>
       <c r="G27" s="24"/>
     </row>
@@ -2011,11 +2011,11 @@
         <v>9</v>
       </c>
       <c r="C28" s="15" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E28" s="43"/>
       <c r="F28" s="43">
-        <v>0.048780487804878</v>
+        <v>0.053571428571429</v>
       </c>
       <c r="G28" s="24"/>
     </row>
@@ -2025,12 +2025,12 @@
         <v>10</v>
       </c>
       <c r="C29" s="48" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D29" s="37"/>
       <c r="E29" s="49"/>
       <c r="F29" s="49">
-        <v>0.048780487804878</v>
+        <v>0.053571428571429</v>
       </c>
       <c r="G29" s="24"/>
     </row>
@@ -2046,7 +2046,7 @@
     <row r="31" spans="1:26" customHeight="1" ht="19.5">
       <c r="A31" s="24"/>
       <c r="B31" s="25" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C31" s="26"/>
       <c r="D31" s="26"/>
@@ -2057,34 +2057,34 @@
     <row r="32" spans="1:26" customHeight="1" ht="15">
       <c r="A32" s="3"/>
       <c r="B32" s="50" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C32" s="50" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D32" s="51" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E32" s="40"/>
       <c r="F32" s="50" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G32" s="3"/>
     </row>
     <row r="33" spans="1:26" customHeight="1" ht="15">
       <c r="A33" s="52"/>
       <c r="B33" s="53" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C33" s="54" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D33" s="55">
         <v>0.57142857142857</v>
       </c>
       <c r="E33" s="27"/>
       <c r="F33" s="54" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G33" s="52"/>
     </row>
@@ -2092,30 +2092,30 @@
       <c r="A34" s="52"/>
       <c r="B34" s="56"/>
       <c r="C34" s="57" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D34" s="58">
         <v>0.42857142857143</v>
       </c>
       <c r="E34" s="59"/>
       <c r="F34" s="57" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G34" s="52"/>
     </row>
     <row r="35" spans="1:26" customHeight="1" ht="15">
       <c r="A35" s="52"/>
       <c r="B35" s="60" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C35" s="54" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D35" s="61">
         <v>0.42857142857143</v>
       </c>
       <c r="F35" s="54" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G35" s="52"/>
     </row>
@@ -2123,14 +2123,14 @@
       <c r="A36" s="52"/>
       <c r="B36" s="62"/>
       <c r="C36" s="44" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D36" s="63">
         <v>0.28571428571429</v>
       </c>
       <c r="E36" s="27"/>
       <c r="F36" s="44" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G36" s="52"/>
     </row>
@@ -2138,13 +2138,13 @@
       <c r="A37" s="52"/>
       <c r="B37" s="62"/>
       <c r="C37" s="54" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D37" s="61">
         <v>0.14285714285714</v>
       </c>
       <c r="F37" s="54" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G37" s="52"/>
     </row>
@@ -2152,30 +2152,30 @@
       <c r="A38" s="52"/>
       <c r="B38" s="64"/>
       <c r="C38" s="65" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D38" s="66">
         <v>0.14285714285714</v>
       </c>
       <c r="E38" s="34"/>
       <c r="F38" s="65" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G38" s="52"/>
     </row>
     <row r="39" spans="1:26" customHeight="1" ht="15">
       <c r="A39" s="52"/>
       <c r="B39" s="67" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C39" s="54" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D39" s="61">
         <v>0.57142857142857</v>
       </c>
       <c r="F39" s="54" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G39" s="52"/>
     </row>
@@ -2183,14 +2183,14 @@
       <c r="A40" s="52"/>
       <c r="B40" s="62"/>
       <c r="C40" s="44" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D40" s="63">
         <v>0.14285714285714</v>
       </c>
       <c r="E40" s="27"/>
       <c r="F40" s="44" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G40" s="52"/>
     </row>
@@ -2198,13 +2198,13 @@
       <c r="A41" s="52"/>
       <c r="B41" s="62"/>
       <c r="C41" s="54" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D41" s="61">
         <v>0.14285714285714</v>
       </c>
       <c r="F41" s="54" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G41" s="52"/>
     </row>
@@ -2212,31 +2212,31 @@
       <c r="A42" s="52"/>
       <c r="B42" s="64"/>
       <c r="C42" s="65" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D42" s="66">
         <v>0.14285714285714</v>
       </c>
       <c r="E42" s="34"/>
       <c r="F42" s="65" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G42" s="52"/>
     </row>
     <row r="43" spans="1:26" customHeight="1" ht="15">
       <c r="A43" s="52"/>
       <c r="B43" s="68" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C43" s="54" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D43" s="55">
         <v>1</v>
       </c>
       <c r="E43" s="27"/>
       <c r="F43" s="54" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G43" s="52"/>
       <c r="H43" s="69"/>
@@ -3367,7 +3367,7 @@
     <row r="1" spans="1:26" customHeight="1" ht="30">
       <c r="A1" s="74"/>
       <c r="B1" s="75" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C1" s="36"/>
       <c r="D1" s="36"/>
@@ -3378,20 +3378,20 @@
     <row r="2" spans="1:26" customHeight="1" ht="30">
       <c r="A2" s="76"/>
       <c r="B2" s="39" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C2" s="40"/>
       <c r="D2" s="77" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E2" s="77" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F2" s="78" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G2" s="77" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H2" s="69"/>
     </row>
@@ -3402,453 +3402,453 @@
       </c>
       <c r="C3"/>
       <c r="D3" s="81" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E3" s="82">
+        <v>2</v>
+      </c>
+      <c r="F3" s="82">
         <v>7</v>
       </c>
-      <c r="F3" s="82">
-        <v>30</v>
-      </c>
       <c r="G3" s="82">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="Z3" s="83"/>
     </row>
     <row r="4" spans="1:26" customHeight="1" ht="19.5">
       <c r="A4" s="79"/>
       <c r="B4" s="84" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C4" s="26"/>
       <c r="D4" s="85" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E4" s="86">
+        <v>0</v>
+      </c>
+      <c r="F4" s="86">
         <v>5</v>
       </c>
-      <c r="F4" s="86">
-        <v>21</v>
-      </c>
       <c r="G4" s="86">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="Z4" s="83"/>
     </row>
     <row r="5" spans="1:26" customHeight="1" ht="19.5">
       <c r="A5" s="79"/>
       <c r="B5" s="80" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C5"/>
       <c r="D5" s="81" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E5" s="82">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F5" s="82">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="G5" s="82">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="Z5" s="83"/>
     </row>
     <row r="6" spans="1:26" customHeight="1" ht="19.5">
       <c r="A6" s="79"/>
       <c r="B6" s="84" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C6" s="26"/>
       <c r="D6" s="85" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E6" s="86">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" s="86">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="G6" s="86">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="Z6" s="83"/>
     </row>
     <row r="7" spans="1:26" customHeight="1" ht="19.5">
       <c r="A7" s="79"/>
       <c r="B7" s="80" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C7"/>
       <c r="D7" s="81" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E7" s="82">
         <v>1</v>
       </c>
       <c r="F7" s="82">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="G7" s="82">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="Z7" s="83"/>
     </row>
     <row r="8" spans="1:26" customHeight="1" ht="19.5">
       <c r="A8" s="79"/>
       <c r="B8" s="84" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C8" s="26"/>
       <c r="D8" s="85" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E8" s="86">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="F8" s="86">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="G8" s="86">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="Z8" s="83"/>
     </row>
     <row r="9" spans="1:26" customHeight="1" ht="19.5">
       <c r="A9" s="79"/>
       <c r="B9" s="80" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C9"/>
       <c r="D9" s="81" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E9" s="82">
+        <v>6</v>
+      </c>
+      <c r="F9" s="82">
+        <v>4</v>
+      </c>
+      <c r="G9" s="82">
         <v>10</v>
-      </c>
-      <c r="F9" s="82">
-        <v>29</v>
-      </c>
-      <c r="G9" s="82">
-        <v>39</v>
       </c>
       <c r="Z9" s="83"/>
     </row>
     <row r="10" spans="1:26" customHeight="1" ht="19.5">
       <c r="A10" s="79"/>
       <c r="B10" s="84" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C10" s="26"/>
       <c r="D10" s="85" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E10" s="86">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F10" s="86">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="G10" s="86">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="Z10" s="83"/>
     </row>
     <row r="11" spans="1:26" customHeight="1" ht="19.5">
       <c r="A11" s="79"/>
       <c r="B11" s="80" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C11"/>
       <c r="D11" s="81" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E11" s="82">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F11" s="82">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="G11" s="82">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="Z11" s="83"/>
     </row>
     <row r="12" spans="1:26" customHeight="1" ht="19.5">
       <c r="A12" s="79"/>
       <c r="B12" s="84" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C12" s="26"/>
       <c r="D12" s="85" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E12" s="86">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="F12" s="86">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="G12" s="86">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="Z12" s="83"/>
     </row>
     <row r="13" spans="1:26" customHeight="1" ht="19.5">
       <c r="A13" s="79"/>
       <c r="B13" s="80" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C13"/>
       <c r="D13" s="81" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E13" s="82">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F13" s="82">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="G13" s="82">
-        <v>47</v>
+        <v>4</v>
       </c>
       <c r="Z13" s="83"/>
     </row>
     <row r="14" spans="1:26" customHeight="1" ht="19.5">
       <c r="A14" s="79"/>
       <c r="B14" s="84" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C14" s="26"/>
       <c r="D14" s="85" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E14" s="86">
+        <v>0</v>
+      </c>
+      <c r="F14" s="86">
         <v>12</v>
       </c>
-      <c r="F14" s="86">
-        <v>35</v>
-      </c>
       <c r="G14" s="86">
-        <v>47</v>
+        <v>12</v>
       </c>
       <c r="Z14" s="83"/>
     </row>
     <row r="15" spans="1:26" customHeight="1" ht="19.5">
       <c r="A15" s="79"/>
       <c r="B15" s="80" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C15"/>
       <c r="D15" s="81" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E15" s="82">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="F15" s="82">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="G15" s="82">
-        <v>51</v>
+        <v>2</v>
       </c>
       <c r="Z15" s="83"/>
     </row>
     <row r="16" spans="1:26" customHeight="1" ht="19.5">
       <c r="A16" s="79"/>
       <c r="B16" s="84" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C16" s="26"/>
       <c r="D16" s="85" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E16" s="86">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="F16" s="86">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="G16" s="86">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="Z16" s="83"/>
     </row>
     <row r="17" spans="1:26" customHeight="1" ht="19.5">
       <c r="A17" s="79"/>
       <c r="B17" s="80" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C17"/>
       <c r="D17" s="81" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E17" s="82">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="F17" s="82">
-        <v>52</v>
+        <v>4</v>
       </c>
       <c r="G17" s="82">
-        <v>71</v>
+        <v>6</v>
       </c>
       <c r="Z17" s="83"/>
     </row>
     <row r="18" spans="1:26" customHeight="1" ht="19.5">
       <c r="A18" s="79"/>
       <c r="B18" s="84" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C18" s="26"/>
       <c r="D18" s="85" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E18" s="86">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F18" s="86">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="G18" s="86">
-        <v>52</v>
+        <v>4</v>
       </c>
       <c r="Z18" s="83"/>
     </row>
     <row r="19" spans="1:26" customHeight="1" ht="19.5">
       <c r="A19" s="79"/>
       <c r="B19" s="80" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C19"/>
       <c r="D19" s="81" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E19" s="82">
+        <v>2</v>
+      </c>
+      <c r="F19" s="82">
+        <v>10</v>
+      </c>
+      <c r="G19" s="82">
         <v>12</v>
-      </c>
-      <c r="F19" s="82">
-        <v>29</v>
-      </c>
-      <c r="G19" s="82">
-        <v>41</v>
       </c>
       <c r="Z19" s="83"/>
     </row>
     <row r="20" spans="1:26" customHeight="1" ht="19.5">
       <c r="A20" s="79"/>
       <c r="B20" s="84" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C20" s="26"/>
       <c r="D20" s="85" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E20" s="86">
+        <v>1</v>
+      </c>
+      <c r="F20" s="86">
+        <v>5</v>
+      </c>
+      <c r="G20" s="86">
         <v>6</v>
-      </c>
-      <c r="F20" s="86">
-        <v>15</v>
-      </c>
-      <c r="G20" s="86">
-        <v>21</v>
       </c>
       <c r="Z20" s="83"/>
     </row>
     <row r="21" spans="1:26" customHeight="1" ht="19.5">
       <c r="A21" s="79"/>
       <c r="B21" s="80" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C21"/>
       <c r="D21" s="81" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E21" s="82">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F21" s="82">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="G21" s="82">
-        <v>39</v>
+        <v>4</v>
       </c>
       <c r="Z21" s="83"/>
     </row>
     <row r="22" spans="1:26" customHeight="1" ht="19.5">
       <c r="A22" s="79"/>
       <c r="B22" s="84" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C22" s="26"/>
       <c r="D22" s="85" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E22" s="86">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="F22" s="86">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="G22" s="86">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="Z22" s="83"/>
     </row>
     <row r="23" spans="1:26" customHeight="1" ht="19.5">
       <c r="A23" s="79"/>
       <c r="B23" s="80" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C23"/>
       <c r="D23" s="81" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E23" s="82">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F23" s="82">
+        <v>7</v>
+      </c>
+      <c r="G23" s="82">
         <v>8</v>
-      </c>
-      <c r="G23" s="82">
-        <v>11</v>
       </c>
       <c r="Z23" s="83"/>
     </row>
     <row r="24" spans="1:26" customHeight="1" ht="19.5">
       <c r="A24" s="79"/>
       <c r="B24" s="84" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C24" s="26"/>
       <c r="D24" s="85" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E24" s="86">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F24" s="86">
         <v>5</v>
       </c>
       <c r="G24" s="86">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Z24" s="83"/>
     </row>
     <row r="25" spans="1:26" customHeight="1" ht="19.5">
       <c r="A25" s="79"/>
       <c r="B25" s="80" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C25"/>
       <c r="D25" s="81" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E25" s="82">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F25" s="82">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G25" s="82">
         <v>9</v>
@@ -3858,11 +3858,11 @@
     <row r="26" spans="1:26" customHeight="1" ht="19.5">
       <c r="A26" s="79"/>
       <c r="B26" s="84" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C26" s="26"/>
       <c r="D26" s="85" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E26" s="86">
         <v>1</v>
@@ -3878,1291 +3878,1291 @@
     <row r="27" spans="1:26" customHeight="1" ht="19.5">
       <c r="A27" s="79"/>
       <c r="B27" s="80" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C27"/>
       <c r="D27" s="81" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E27" s="82">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F27" s="82">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="G27" s="82">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="Z27" s="83"/>
     </row>
     <row r="28" spans="1:26" customHeight="1" ht="19.5">
       <c r="A28" s="79"/>
       <c r="B28" s="84" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C28" s="26"/>
       <c r="D28" s="85" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E28" s="86">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F28" s="86">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G28" s="86">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="Z28" s="83"/>
     </row>
     <row r="29" spans="1:26" customHeight="1" ht="19.5">
       <c r="A29" s="79"/>
       <c r="B29" s="80" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C29"/>
       <c r="D29" s="81" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E29" s="82">
+        <v>2</v>
+      </c>
+      <c r="F29" s="82">
         <v>4</v>
       </c>
-      <c r="F29" s="82">
-        <v>3</v>
-      </c>
       <c r="G29" s="82">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z29" s="83"/>
     </row>
     <row r="30" spans="1:26" customHeight="1" ht="19.5">
       <c r="A30" s="79"/>
       <c r="B30" s="84" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C30" s="26"/>
       <c r="D30" s="85" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E30" s="86">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F30" s="86">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="G30" s="86">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="Z30" s="83"/>
     </row>
     <row r="31" spans="1:26" customHeight="1" ht="19.5">
       <c r="A31" s="79"/>
       <c r="B31" s="80" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C31"/>
       <c r="D31" s="81" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E31" s="82">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F31" s="82">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="G31" s="82">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="Z31" s="83"/>
     </row>
     <row r="32" spans="1:26" customHeight="1" ht="19.5">
       <c r="A32" s="79"/>
       <c r="B32" s="84" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C32" s="26"/>
       <c r="D32" s="85" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E32" s="86">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F32" s="86">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G32" s="86">
-        <v>46</v>
+        <v>16</v>
       </c>
       <c r="Z32" s="83"/>
     </row>
     <row r="33" spans="1:26" customHeight="1" ht="19.5">
       <c r="A33" s="79"/>
       <c r="B33" s="80" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C33"/>
       <c r="D33" s="81" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E33" s="82">
         <v>0</v>
       </c>
       <c r="F33" s="82">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G33" s="82">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z33" s="83"/>
     </row>
     <row r="34" spans="1:26" customHeight="1" ht="19.5">
       <c r="A34" s="79"/>
       <c r="B34" s="84" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C34" s="26"/>
       <c r="D34" s="85" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E34" s="86">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F34" s="86">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G34" s="86">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Z34" s="83"/>
     </row>
     <row r="35" spans="1:26" customHeight="1" ht="19.5">
       <c r="A35" s="79"/>
       <c r="B35" s="80" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C35"/>
       <c r="D35" s="81" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E35" s="82">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F35" s="82">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G35" s="82">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Z35" s="83"/>
     </row>
     <row r="36" spans="1:26" customHeight="1" ht="19.5">
       <c r="A36" s="79"/>
       <c r="B36" s="84" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C36" s="26"/>
       <c r="D36" s="85" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E36" s="86">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F36" s="86">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G36" s="86">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Z36" s="83"/>
     </row>
     <row r="37" spans="1:26" customHeight="1" ht="19.5">
       <c r="A37" s="79"/>
       <c r="B37" s="80" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C37"/>
       <c r="D37" s="81" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E37" s="82">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F37" s="82">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G37" s="82">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Z37" s="83"/>
     </row>
     <row r="38" spans="1:26" customHeight="1" ht="19.5">
       <c r="A38" s="79"/>
       <c r="B38" s="84" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C38" s="26"/>
       <c r="D38" s="85" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E38" s="86">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F38" s="86">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G38" s="86">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Z38" s="83"/>
     </row>
     <row r="39" spans="1:26" customHeight="1" ht="19.5">
       <c r="A39" s="79"/>
       <c r="B39" s="80" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C39"/>
       <c r="D39" s="81" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E39" s="82">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F39" s="82">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G39" s="82">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z39" s="83"/>
     </row>
     <row r="40" spans="1:26" customHeight="1" ht="19.5">
       <c r="A40" s="79"/>
       <c r="B40" s="84" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C40" s="26"/>
       <c r="D40" s="85" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E40" s="86">
         <v>0</v>
       </c>
       <c r="F40" s="86">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G40" s="86">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Z40" s="83"/>
     </row>
     <row r="41" spans="1:26" customHeight="1" ht="19.5">
       <c r="A41" s="79"/>
       <c r="B41" s="80" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C41"/>
       <c r="D41" s="81" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E41" s="82">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F41" s="82">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G41" s="82">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z41" s="83"/>
     </row>
     <row r="42" spans="1:26" customHeight="1" ht="19.5">
       <c r="A42" s="79"/>
       <c r="B42" s="84" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C42" s="26"/>
       <c r="D42" s="85" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E42" s="86">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F42" s="86">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G42" s="86">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Z42" s="83"/>
     </row>
     <row r="43" spans="1:26" customHeight="1" ht="19.5">
       <c r="A43" s="79"/>
       <c r="B43" s="80" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C43"/>
       <c r="D43" s="81" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E43" s="82">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F43" s="82">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G43" s="82">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z43" s="83"/>
     </row>
     <row r="44" spans="1:26" customHeight="1" ht="19.5">
       <c r="A44" s="79"/>
       <c r="B44" s="84" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C44" s="26"/>
       <c r="D44" s="85" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E44" s="86">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F44" s="86">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G44" s="86">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Z44" s="83"/>
     </row>
     <row r="45" spans="1:26" customHeight="1" ht="19.5">
       <c r="A45" s="79"/>
       <c r="B45" s="80" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C45"/>
       <c r="D45" s="81" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E45" s="82">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F45" s="82">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G45" s="82">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Z45" s="83"/>
     </row>
     <row r="46" spans="1:26" customHeight="1" ht="19.5">
       <c r="A46" s="79"/>
       <c r="B46" s="84" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C46" s="26"/>
       <c r="D46" s="85" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E46" s="86">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F46" s="86">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G46" s="86">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z46" s="83"/>
     </row>
     <row r="47" spans="1:26" customHeight="1" ht="19.5">
       <c r="A47" s="79"/>
       <c r="B47" s="80" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C47"/>
       <c r="D47" s="81" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E47" s="82">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F47" s="82">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G47" s="82">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="Z47" s="83"/>
     </row>
     <row r="48" spans="1:26" customHeight="1" ht="19.5">
       <c r="A48" s="79"/>
       <c r="B48" s="84" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C48" s="26"/>
       <c r="D48" s="85" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E48" s="86">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F48" s="86">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G48" s="86">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="Z48" s="83"/>
     </row>
     <row r="49" spans="1:26" customHeight="1" ht="19.5">
       <c r="A49" s="79"/>
       <c r="B49" s="80" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C49"/>
       <c r="D49" s="81" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E49" s="82">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F49" s="82">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G49" s="82">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="Z49" s="83"/>
     </row>
     <row r="50" spans="1:26" customHeight="1" ht="19.5">
       <c r="A50" s="79"/>
       <c r="B50" s="84" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C50" s="26"/>
       <c r="D50" s="85" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E50" s="86">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F50" s="86">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G50" s="86">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z50" s="83"/>
     </row>
     <row r="51" spans="1:26" customHeight="1" ht="19.5">
       <c r="A51" s="79"/>
       <c r="B51" s="80" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C51"/>
       <c r="D51" s="81" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E51" s="82">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F51" s="82">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="G51" s="82">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="Z51" s="83"/>
     </row>
     <row r="52" spans="1:26" customHeight="1" ht="19.5">
       <c r="A52" s="79"/>
       <c r="B52" s="84" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C52" s="26"/>
       <c r="D52" s="85" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E52" s="86">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F52" s="86">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G52" s="86">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z52" s="83"/>
     </row>
     <row r="53" spans="1:26" customHeight="1" ht="19.5">
       <c r="A53" s="79"/>
       <c r="B53" s="80" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C53"/>
       <c r="D53" s="81" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E53" s="82">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F53" s="82">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="G53" s="82">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="Z53" s="83"/>
     </row>
     <row r="54" spans="1:26" customHeight="1" ht="19.5">
       <c r="A54" s="79"/>
       <c r="B54" s="84" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C54" s="26"/>
       <c r="D54" s="85" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E54" s="86">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F54" s="86">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="G54" s="86">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="Z54" s="83"/>
     </row>
     <row r="55" spans="1:26" customHeight="1" ht="19.5">
       <c r="A55" s="79"/>
       <c r="B55" s="80" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C55"/>
       <c r="D55" s="81" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E55" s="82">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F55" s="82">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G55" s="82">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="Z55" s="83"/>
     </row>
     <row r="56" spans="1:26" customHeight="1" ht="19.5">
       <c r="A56" s="79"/>
       <c r="B56" s="84" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C56" s="26"/>
       <c r="D56" s="85" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E56" s="86">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F56" s="86">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G56" s="86">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="Z56" s="83"/>
     </row>
     <row r="57" spans="1:26" customHeight="1" ht="19.5">
       <c r="A57" s="79"/>
       <c r="B57" s="80" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C57"/>
       <c r="D57" s="81" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E57" s="82">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F57" s="82">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G57" s="82">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="Z57" s="83"/>
     </row>
     <row r="58" spans="1:26" customHeight="1" ht="19.5">
       <c r="A58" s="79"/>
       <c r="B58" s="84" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C58" s="26"/>
       <c r="D58" s="85" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E58" s="86">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F58" s="86">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G58" s="86">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="Z58" s="83"/>
     </row>
     <row r="59" spans="1:26" customHeight="1" ht="19.5">
       <c r="A59" s="79"/>
       <c r="B59" s="80" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C59"/>
       <c r="D59" s="81" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E59" s="82">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F59" s="82">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G59" s="82">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="Z59" s="83"/>
     </row>
     <row r="60" spans="1:26" customHeight="1" ht="19.5">
       <c r="A60" s="79"/>
       <c r="B60" s="84" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C60" s="26"/>
       <c r="D60" s="85" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E60" s="86">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F60" s="86">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G60" s="86">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="Z60" s="83"/>
     </row>
     <row r="61" spans="1:26" customHeight="1" ht="19.5">
       <c r="A61" s="79"/>
       <c r="B61" s="80" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C61"/>
       <c r="D61" s="81" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E61" s="82">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F61" s="82">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G61" s="82">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="Z61" s="83"/>
     </row>
     <row r="62" spans="1:26" customHeight="1" ht="19.5">
       <c r="A62" s="79"/>
       <c r="B62" s="84" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C62" s="26"/>
       <c r="D62" s="85" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E62" s="86">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F62" s="86">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G62" s="86">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="Z62" s="83"/>
     </row>
     <row r="63" spans="1:26" customHeight="1" ht="19.5">
       <c r="A63" s="79"/>
       <c r="B63" s="80" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C63"/>
       <c r="D63" s="81" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E63" s="82">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F63" s="82">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G63" s="82">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="Z63" s="83"/>
     </row>
     <row r="64" spans="1:26" customHeight="1" ht="19.5">
       <c r="A64" s="79"/>
       <c r="B64" s="84" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C64" s="26"/>
       <c r="D64" s="85" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E64" s="86">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F64" s="86">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G64" s="86">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Z64" s="83"/>
     </row>
     <row r="65" spans="1:26" customHeight="1" ht="19.5">
       <c r="A65" s="79"/>
       <c r="B65" s="80" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C65"/>
       <c r="D65" s="81" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E65" s="82">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F65" s="82">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G65" s="82">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="Z65" s="83"/>
     </row>
     <row r="66" spans="1:26" customHeight="1" ht="19.5">
       <c r="A66" s="79"/>
       <c r="B66" s="84" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C66" s="26"/>
       <c r="D66" s="85" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E66" s="86">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F66" s="86">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G66" s="86">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="Z66" s="83"/>
     </row>
     <row r="67" spans="1:26" customHeight="1" ht="19.5">
       <c r="A67" s="79"/>
       <c r="B67" s="80" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C67"/>
       <c r="D67" s="81" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E67" s="82">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F67" s="82">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="G67" s="82">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="Z67" s="83"/>
     </row>
     <row r="68" spans="1:26" customHeight="1" ht="19.5">
       <c r="A68" s="79"/>
       <c r="B68" s="84" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C68" s="26"/>
       <c r="D68" s="85" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E68" s="86">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F68" s="86">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G68" s="86">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="Z68" s="83"/>
     </row>
     <row r="69" spans="1:26" customHeight="1" ht="19.5">
       <c r="A69" s="79"/>
       <c r="B69" s="80" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C69"/>
       <c r="D69" s="81" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E69" s="82">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F69" s="82">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="G69" s="82">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="Z69" s="83"/>
     </row>
     <row r="70" spans="1:26" customHeight="1" ht="19.5">
       <c r="A70" s="79"/>
       <c r="B70" s="84" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C70" s="26"/>
       <c r="D70" s="85" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E70" s="86">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F70" s="86">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G70" s="86">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="Z70" s="83"/>
     </row>
     <row r="71" spans="1:26" customHeight="1" ht="19.5">
       <c r="A71" s="79"/>
       <c r="B71" s="80" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C71"/>
       <c r="D71" s="81" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E71" s="82">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F71" s="82">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="G71" s="82">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="Z71" s="83"/>
     </row>
     <row r="72" spans="1:26" customHeight="1" ht="19.5">
       <c r="A72" s="79"/>
       <c r="B72" s="84" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C72" s="26"/>
       <c r="D72" s="85" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E72" s="86">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F72" s="86">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="G72" s="86">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="Z72" s="83"/>
     </row>
     <row r="73" spans="1:26" customHeight="1" ht="19.5">
       <c r="A73" s="79"/>
       <c r="B73" s="80" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C73"/>
       <c r="D73" s="81" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E73" s="82">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F73" s="82">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="G73" s="82">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="Z73" s="83"/>
     </row>
     <row r="74" spans="1:26" customHeight="1" ht="19.5">
       <c r="A74" s="79"/>
       <c r="B74" s="84" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C74" s="26"/>
       <c r="D74" s="85" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E74" s="86">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F74" s="86">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="G74" s="86">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="Z74" s="83"/>
     </row>
     <row r="75" spans="1:26" customHeight="1" ht="19.5">
       <c r="A75" s="79"/>
       <c r="B75" s="80" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C75"/>
       <c r="D75" s="81" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E75" s="82">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F75" s="82">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="G75" s="82">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="Z75" s="83"/>
     </row>
     <row r="76" spans="1:26" customHeight="1" ht="19.5">
       <c r="A76" s="79"/>
       <c r="B76" s="84" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C76" s="26"/>
       <c r="D76" s="85" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E76" s="86">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F76" s="86">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="G76" s="86">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="Z76" s="83"/>
     </row>
     <row r="77" spans="1:26" customHeight="1" ht="19.5">
       <c r="A77" s="79"/>
       <c r="B77" s="80" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C77"/>
       <c r="D77" s="81" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E77" s="82">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F77" s="82">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="G77" s="82">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="Z77" s="83"/>
     </row>
     <row r="78" spans="1:26" customHeight="1" ht="19.5">
       <c r="A78" s="79"/>
       <c r="B78" s="84" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C78" s="26"/>
       <c r="D78" s="85" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E78" s="86">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F78" s="86">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G78" s="86">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="Z78" s="83"/>
     </row>
     <row r="79" spans="1:26" customHeight="1" ht="19.5">
       <c r="A79" s="79"/>
       <c r="B79" s="80" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C79"/>
       <c r="D79" s="81" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E79" s="82">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F79" s="82">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="G79" s="82">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="Z79" s="83"/>
     </row>
     <row r="80" spans="1:26" customHeight="1" ht="19.5">
       <c r="A80" s="79"/>
       <c r="B80" s="84" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C80" s="26"/>
       <c r="D80" s="85" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E80" s="86">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F80" s="86">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G80" s="86">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="Z80" s="83"/>
     </row>
     <row r="81" spans="1:26" customHeight="1" ht="19.5">
       <c r="A81" s="79"/>
       <c r="B81" s="80" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C81"/>
       <c r="D81" s="81" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E81" s="82">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F81" s="82">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G81" s="82">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z81" s="83"/>
     </row>
     <row r="82" spans="1:26" customHeight="1" ht="19.5">
       <c r="A82" s="79"/>
       <c r="B82" s="84" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C82" s="26"/>
       <c r="D82" s="85" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E82" s="86">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F82" s="86">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G82" s="86">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z82" s="83"/>
     </row>
     <row r="83" spans="1:26" customHeight="1" ht="19.5">
       <c r="A83" s="79"/>
       <c r="B83" s="80" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C83"/>
       <c r="D83" s="81" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E83" s="82">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F83" s="82">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G83" s="82">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z83" s="83"/>
     </row>
     <row r="84" spans="1:26" customHeight="1" ht="19.5">
       <c r="A84" s="79"/>
       <c r="B84" s="84" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C84" s="26"/>
       <c r="D84" s="85" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E84" s="86">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F84" s="86">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G84" s="86">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Z84" s="83"/>
     </row>
     <row r="85" spans="1:26" customHeight="1" ht="19.5">
       <c r="A85" s="79"/>
       <c r="B85" s="80" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C85"/>
       <c r="D85" s="81" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E85" s="82">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F85" s="82">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G85" s="82">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z85" s="83"/>
     </row>
     <row r="86" spans="1:26" customHeight="1" ht="19.5">
       <c r="A86" s="79"/>
       <c r="B86" s="84" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C86" s="26"/>
       <c r="D86" s="85" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E86" s="86">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F86" s="86">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G86" s="86">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z86" s="83"/>
     </row>
     <row r="87" spans="1:26" customHeight="1" ht="19.5">
       <c r="A87" s="79"/>
       <c r="B87" s="80" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C87"/>
       <c r="D87" s="81" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E87" s="82">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F87" s="82">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G87" s="82">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Z87" s="83"/>
     </row>
     <row r="88" spans="1:26" customHeight="1" ht="19.5">
       <c r="A88" s="79"/>
       <c r="B88" s="84" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C88" s="26"/>
       <c r="D88" s="85" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E88" s="86">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F88" s="86">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G88" s="86">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="Z88" s="83"/>
     </row>
     <row r="89" spans="1:26" customHeight="1" ht="19.5">
       <c r="A89" s="79"/>
       <c r="B89" s="80" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C89"/>
       <c r="D89" s="81" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E89" s="82">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F89" s="82">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G89" s="82">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Z89" s="83"/>
     </row>
     <row r="90" spans="1:26" customHeight="1" ht="19.5">
       <c r="A90" s="79"/>
       <c r="B90" s="84" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C90" s="26"/>
       <c r="D90" s="85" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E90" s="86">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F90" s="86">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G90" s="86">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="Z90" s="83"/>
     </row>
     <row r="91" spans="1:26" customHeight="1" ht="19.5">
       <c r="A91" s="79"/>
       <c r="B91" s="80" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C91"/>
       <c r="D91" s="81" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E91" s="82">
         <v>0</v>
@@ -5178,11 +5178,11 @@
     <row r="92" spans="1:26" customHeight="1" ht="19.5">
       <c r="A92" s="79"/>
       <c r="B92" s="84" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C92" s="26"/>
       <c r="D92" s="85" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E92" s="86">
         <v>0</v>
@@ -5198,11 +5198,11 @@
     <row r="93" spans="1:26" customHeight="1" ht="19.5">
       <c r="A93" s="79"/>
       <c r="B93" s="80" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C93"/>
       <c r="D93" s="81" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E93" s="82">
         <v>0</v>
@@ -5218,11 +5218,11 @@
     <row r="94" spans="1:26" customHeight="1" ht="19.5">
       <c r="A94" s="79"/>
       <c r="B94" s="84" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C94" s="26"/>
       <c r="D94" s="85" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E94" s="86">
         <v>0</v>
@@ -13515,7 +13515,7 @@
     <row r="1" spans="1:26" customHeight="1" ht="30">
       <c r="A1" s="89"/>
       <c r="B1" s="90" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C1" s="26"/>
       <c r="D1" s="26"/>
@@ -13527,19 +13527,19 @@
     <row r="2" spans="1:26" customHeight="1" ht="24.75">
       <c r="A2" s="83"/>
       <c r="B2" s="91" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C2" s="92" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D2" s="91" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E2" s="91" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F2" s="91" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G2" s="83"/>
       <c r="H2" s="89"/>
@@ -13547,13 +13547,13 @@
     <row r="3" spans="1:26" customHeight="1" ht="27.75">
       <c r="A3" s="89"/>
       <c r="B3" s="93" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C3" s="24" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D3" s="94" t="s">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="E3" s="24">
         <v>11</v>
@@ -13568,7 +13568,7 @@
     <row r="4" spans="1:26" customHeight="1" ht="15">
       <c r="A4" s="89"/>
       <c r="B4" s="96" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C4"/>
       <c r="D4"/>
@@ -13581,13 +13581,13 @@
     <row r="5" spans="1:26" customHeight="1" ht="27.75">
       <c r="A5" s="89"/>
       <c r="B5" s="97" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C5" s="98" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D5" s="99" t="s">
-        <v>86</v>
+        <v>145</v>
       </c>
       <c r="E5" s="98">
         <v>4</v>
@@ -13602,7 +13602,7 @@
     <row r="6" spans="1:26" customHeight="1" ht="15">
       <c r="A6" s="95"/>
       <c r="B6" s="100" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C6" s="26"/>
       <c r="D6" s="26"/>
@@ -13615,13 +13615,13 @@
     <row r="7" spans="1:26" customHeight="1" ht="27.75">
       <c r="A7" s="89"/>
       <c r="B7" s="93" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C7" s="24" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D7" s="94" t="s">
-        <v>96</v>
+        <v>155</v>
       </c>
       <c r="E7" s="24">
         <v>111</v>
@@ -13636,7 +13636,7 @@
     <row r="8" spans="1:26" customHeight="1" ht="15">
       <c r="A8" s="89"/>
       <c r="B8" s="96" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C8"/>
       <c r="D8"/>
@@ -13649,13 +13649,13 @@
     <row r="9" spans="1:26" customHeight="1" ht="27.75">
       <c r="A9" s="89"/>
       <c r="B9" s="97" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C9" s="98" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D9" s="99" t="s">
-        <v>86</v>
+        <v>145</v>
       </c>
       <c r="E9" s="98">
         <v>0</v>
@@ -13670,7 +13670,7 @@
     <row r="10" spans="1:26" customHeight="1" ht="15">
       <c r="A10" s="95"/>
       <c r="B10" s="100" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C10" s="26"/>
       <c r="D10" s="26"/>
@@ -13683,7 +13683,7 @@
     <row r="11" spans="1:26" customHeight="1" ht="24">
       <c r="A11" s="89"/>
       <c r="B11" s="101" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C11" s="26"/>
       <c r="D11" s="27"/>
@@ -23647,15 +23647,15 @@
   <sheetData>
     <row r="1" spans="1:26" customHeight="1" ht="30">
       <c r="A1" s="103" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="2" spans="1:26" customHeight="1" ht="18">
       <c r="A2" s="104" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B2" s="105" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C2" s="106"/>
       <c r="D2" s="106"/>
@@ -23678,7 +23678,7 @@
       <c r="U2" s="106"/>
       <c r="V2" s="107"/>
       <c r="W2" s="108" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="3" spans="1:26" customHeight="1" ht="24.75">
@@ -23750,7 +23750,7 @@
     </row>
     <row r="4" spans="1:26" customHeight="1" ht="18">
       <c r="A4" s="112" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B4" s="113">
         <v>0</v>
@@ -23823,7 +23823,7 @@
     </row>
     <row r="5" spans="1:26" customHeight="1" ht="18">
       <c r="A5" s="114" t="s">
-        <v>182</v>
+        <v>31</v>
       </c>
       <c r="B5" s="115">
         <v>0</v>
